--- a/src/main/resources/Data/Data.xlsx
+++ b/src/main/resources/Data/Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dev\Github\tools\Templater\src\main\resources\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{40BE65A8-CD55-4CE0-93ED-A30CDDDC559B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{394F5404-DE25-4EA2-A7D2-9E8463A1926F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1950" yWindow="1950" windowWidth="18555" windowHeight="7785" xr2:uid="{84B44657-EAC1-439B-8DEB-42FCDBD8EFEF}"/>
+    <workbookView xWindow="4890" yWindow="3045" windowWidth="14895" windowHeight="7125" xr2:uid="{84B44657-EAC1-439B-8DEB-42FCDBD8EFEF}"/>
   </bookViews>
   <sheets>
     <sheet name="Blad1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
     <t>Naam</t>
   </si>
@@ -67,6 +67,30 @@
   </si>
   <si>
     <t>Weg 3, Utrecht</t>
+  </si>
+  <si>
+    <t>Prefix</t>
+  </si>
+  <si>
+    <t>JanJ</t>
+  </si>
+  <si>
+    <t>PieterP</t>
+  </si>
+  <si>
+    <t>MarieV</t>
+  </si>
+  <si>
+    <t>txt</t>
+  </si>
+  <si>
+    <t>csv</t>
+  </si>
+  <si>
+    <t>som</t>
+  </si>
+  <si>
+    <t>Ext</t>
   </si>
 </sst>
 </file>
@@ -442,80 +466,104 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E6D96B4-DE4C-498F-8941-935F82755F76}">
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="18" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20" customWidth="1"/>
-    <col min="2" max="2" width="32" customWidth="1"/>
-    <col min="3" max="3" width="24.28515625" customWidth="1"/>
-    <col min="4" max="4" width="22" customWidth="1"/>
+    <col min="3" max="3" width="20" customWidth="1"/>
+    <col min="4" max="4" width="32" customWidth="1"/>
+    <col min="5" max="5" width="24.28515625" customWidth="1"/>
+    <col min="6" max="6" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="2">
+      <c r="F2" s="2">
         <v>612345678</v>
       </c>
-      <c r="E2" s="2">
+      <c r="G2" s="2">
         <v>32</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
+    <row r="3" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="D3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="E3" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="2">
+      <c r="F3" s="2">
         <v>687654321</v>
       </c>
-      <c r="E3" s="2">
+      <c r="G3" s="2">
         <v>45</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
+    <row r="4" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="D4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="2">
+      <c r="F4" s="2">
         <v>611122233</v>
       </c>
-      <c r="E4" s="2">
+      <c r="G4" s="2">
         <v>28</v>
       </c>
     </row>
